--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N58_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N58_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.76211667077852</v>
+        <v>6.786343959001511</v>
       </c>
       <c r="D2" t="n">
-        <v>41.41984362547084</v>
+        <v>6.730724589139012</v>
       </c>
       <c r="E2" t="n">
-        <v>12.36292102405498</v>
+        <v>2.008974666408935</v>
       </c>
       <c r="F2" t="n">
-        <v>12.45515096616468</v>
+        <v>2.023962032001761</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.47460789892373</v>
+        <v>3.327123783575106</v>
       </c>
       <c r="D3" t="n">
-        <v>20.1774252187044</v>
+        <v>3.278831598039464</v>
       </c>
       <c r="E3" t="n">
-        <v>12.36292102405498</v>
+        <v>2.008974666408935</v>
       </c>
       <c r="F3" t="n">
-        <v>12.45515096616468</v>
+        <v>2.023962032001761</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.51388094292618</v>
+        <v>8.533505653225504</v>
       </c>
       <c r="D4" t="n">
-        <v>52.29470292686709</v>
+        <v>8.497889225615902</v>
       </c>
       <c r="E4" t="n">
-        <v>12.36292102405498</v>
+        <v>2.008974666408935</v>
       </c>
       <c r="F4" t="n">
-        <v>12.45515096616468</v>
+        <v>2.023962032001761</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>48.55291589421481</v>
+        <v>7.889848832809906</v>
       </c>
       <c r="D5" t="n">
-        <v>48.72496937901609</v>
+        <v>7.917807524090114</v>
       </c>
       <c r="E5" t="n">
-        <v>12.36292102405498</v>
+        <v>2.008974666408935</v>
       </c>
       <c r="F5" t="n">
-        <v>12.45515096616468</v>
+        <v>2.023962032001761</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
